--- a/LISTAS/mi/PORTACANDADOS.xlsx
+++ b/LISTAS/mi/PORTACANDADOS.xlsx
@@ -723,14 +723,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45163.60909743008</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -771,25 +767,6 @@
     <row r="11" ht="17.25" customHeight="1" s="15">
       <c r="E11" s="8" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="18" customHeight="1" s="15">
       <c r="A31" s="12" t="inlineStr">
         <is>
@@ -821,7 +798,7 @@
       </c>
       <c r="C32" s="17" t="n"/>
       <c r="D32" s="11" t="n">
-        <v>96.72499999999999</v>
+        <v>111.234</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="15">
@@ -837,7 +814,7 @@
       </c>
       <c r="C33" s="17" t="n"/>
       <c r="D33" s="10" t="n">
-        <v>138.403</v>
+        <v>159.163</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="15">
@@ -853,7 +830,7 @@
       </c>
       <c r="C34" s="17" t="n"/>
       <c r="D34" s="11" t="n">
-        <v>184.272</v>
+        <v>211.913</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="15">
@@ -869,7 +846,7 @@
       </c>
       <c r="C35" s="17" t="n"/>
       <c r="D35" s="10" t="n">
-        <v>189.717</v>
+        <v>218.175</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="15">
@@ -885,7 +862,7 @@
       </c>
       <c r="C36" s="17" t="n"/>
       <c r="D36" s="11" t="n">
-        <v>248.635</v>
+        <v>285.93</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="15">
@@ -901,7 +878,7 @@
       </c>
       <c r="C37" s="17" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>284.302</v>
+        <v>326.947</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="15">
@@ -917,7 +894,7 @@
       </c>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="11" t="n">
-        <v>340.449</v>
+        <v>391.516</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="15">
@@ -933,16 +910,9 @@
       </c>
       <c r="C39" s="17" t="n"/>
       <c r="D39" s="11" t="n">
-        <v>405.401</v>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
+        <v>466.211</v>
+      </c>
+    </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
@@ -952,18 +922,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/PORTACANDADOS.xlsx
+++ b/LISTAS/mi/PORTACANDADOS.xlsx
@@ -723,7 +723,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/PORTACANDADOS.xlsx
+++ b/LISTAS/mi/PORTACANDADOS.xlsx
@@ -723,7 +723,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/PORTACANDADOS.xlsx
+++ b/LISTAS/mi/PORTACANDADOS.xlsx
@@ -723,10 +723,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45266</v>
+        <v>45261.57774937743</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -767,6 +771,25 @@
     <row r="11" ht="17.25" customHeight="1" s="15">
       <c r="E11" s="8" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="18" customHeight="1" s="15">
       <c r="A31" s="12" t="inlineStr">
         <is>
@@ -798,7 +821,7 @@
       </c>
       <c r="C32" s="17" t="n"/>
       <c r="D32" s="11" t="n">
-        <v>111.234</v>
+        <v>170.26</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="15">
@@ -814,7 +837,7 @@
       </c>
       <c r="C33" s="17" t="n"/>
       <c r="D33" s="10" t="n">
-        <v>159.163</v>
+        <v>243.62</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="15">
@@ -830,7 +853,7 @@
       </c>
       <c r="C34" s="17" t="n"/>
       <c r="D34" s="11" t="n">
-        <v>211.913</v>
+        <v>324.36</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="15">
@@ -846,7 +869,7 @@
       </c>
       <c r="C35" s="17" t="n"/>
       <c r="D35" s="10" t="n">
-        <v>218.175</v>
+        <v>333.95</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="15">
@@ -862,7 +885,7 @@
       </c>
       <c r="C36" s="17" t="n"/>
       <c r="D36" s="11" t="n">
-        <v>285.93</v>
+        <v>437.65</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="15">
@@ -878,7 +901,7 @@
       </c>
       <c r="C37" s="17" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>326.947</v>
+        <v>500.44</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="15">
@@ -894,7 +917,7 @@
       </c>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="11" t="n">
-        <v>391.516</v>
+        <v>599.27</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="15">
@@ -910,9 +933,16 @@
       </c>
       <c r="C39" s="17" t="n"/>
       <c r="D39" s="11" t="n">
-        <v>466.211</v>
-      </c>
-    </row>
+        <v>713.6</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
@@ -922,18 +952,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/PORTACANDADOS.xlsx
+++ b/LISTAS/mi/PORTACANDADOS.xlsx
@@ -723,14 +723,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45261.57774937743</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -771,25 +767,6 @@
     <row r="11" ht="17.25" customHeight="1" s="15">
       <c r="E11" s="8" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="18" customHeight="1" s="15">
       <c r="A31" s="12" t="inlineStr">
         <is>
@@ -821,7 +798,7 @@
       </c>
       <c r="C32" s="17" t="n"/>
       <c r="D32" s="11" t="n">
-        <v>170.26</v>
+        <v>111.234</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="15">
@@ -837,7 +814,7 @@
       </c>
       <c r="C33" s="17" t="n"/>
       <c r="D33" s="10" t="n">
-        <v>243.62</v>
+        <v>159.163</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="15">
@@ -853,7 +830,7 @@
       </c>
       <c r="C34" s="17" t="n"/>
       <c r="D34" s="11" t="n">
-        <v>324.36</v>
+        <v>211.913</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="15">
@@ -869,7 +846,7 @@
       </c>
       <c r="C35" s="17" t="n"/>
       <c r="D35" s="10" t="n">
-        <v>333.95</v>
+        <v>218.175</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="15">
@@ -885,7 +862,7 @@
       </c>
       <c r="C36" s="17" t="n"/>
       <c r="D36" s="11" t="n">
-        <v>437.65</v>
+        <v>285.93</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="15">
@@ -901,7 +878,7 @@
       </c>
       <c r="C37" s="17" t="n"/>
       <c r="D37" s="10" t="n">
-        <v>500.44</v>
+        <v>326.947</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="15">
@@ -917,7 +894,7 @@
       </c>
       <c r="C38" s="17" t="n"/>
       <c r="D38" s="11" t="n">
-        <v>599.27</v>
+        <v>391.516</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="15">
@@ -933,16 +910,9 @@
       </c>
       <c r="C39" s="17" t="n"/>
       <c r="D39" s="11" t="n">
-        <v>713.6</v>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
+        <v>466.211</v>
+      </c>
+    </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
@@ -952,18 +922,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
